--- a/endpoint_excels/iss__securities__security__indices.xlsx
+++ b/endpoint_excels/iss__securities__security__indices.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +28,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +61,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -134,6 +161,23 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__securities__s" displayName="TBL_01_iss__securities__s" ref="A1:H15" headerRowCount="1">
+  <autoFilter ref="A1:H15"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="SHORTNAME"/>
+    <tableColumn id="4" name="FROM"/>
+    <tableColumn id="5" name="TILL"/>
+    <tableColumn id="6" name="CURRENTVALUE"/>
+    <tableColumn id="7" name="LASTCHANGEPRC"/>
+    <tableColumn id="8" name="LASTCHANGE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,8 +471,18 @@
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -471,510 +525,513 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>BPSIG</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Субиндекс облигаций ОФЗ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2021-12-17</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>2457.18</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.83</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>20.17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RGBILP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>RGBILP</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>117.79</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>RUABICP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>ABI CP</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>92.44</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.31</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.29</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>RUABITR</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ABI TR</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>285.05</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>RUGBICP10Y</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>RUGBICP10Y</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>98.62</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>RUGBICP5+</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>RUGBICP5+</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>103.61</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>RUGBICP5Y7Y</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>RUGBICP5Y7Y</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="2" t="n">
         <v>85.2</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.85</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.72</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>RUGBICP7Y+</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>RUGBICP7Y+</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>81.01000000000001</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="2" t="n">
         <v>1.61</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>1.28</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>RUGBITR10Y</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>RUGBITR10Y</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>622.45</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.99</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="2" t="n">
         <v>6.12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>RUGBITR5+</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>RUGBITR5+</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>653.46</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="2" t="n">
         <v>0.99</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="2" t="n">
         <v>6.43</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>RUGBITR5Y7Y</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>RUGBITR5Y7Y</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="2" t="n">
         <v>120.11</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="2" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>RUGBITR7Y+</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>RUGBITR7Y+</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>115.19</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="2" t="n">
         <v>1.87</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>RGBI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Индекс Мосбиржи гос обл RGBI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>118.27</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="2" t="n">
         <v>0.74</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.87</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/indices.json</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>RGBITR</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Индекс Мосбиржи гос обл RGBITR</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>754.74</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="2" t="n">
         <v>6.09</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>